--- a/main/ig/StructureDefinition-dmi-procedure.xlsx
+++ b/main/ig/StructureDefinition-dmi-procedure.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-procedure.xlsx
+++ b/main/ig/StructureDefinition-dmi-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-procedure.xlsx
+++ b/main/ig/StructureDefinition-dmi-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Procedure.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Procedure.language</t>
   </si>
   <si>
@@ -416,9 +426,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Procedure.extension</t>
   </si>
   <si>
@@ -439,6 +446,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -485,9 +502,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -525,9 +539,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Procedure.identifier:idIntervention.extension</t>
   </si>
   <si>
@@ -535,13 +546,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -698,7 +702,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -727,6 +739,10 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
@@ -786,6 +802,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -824,6 +843,9 @@
     <t>A reference to a resource that contains details of the request for this procedure.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -915,6 +937,9 @@
     <t>.reason.Observation.value</t>
   </si>
   <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
     <t>Procedure.category</t>
   </si>
   <si>
@@ -922,6 +947,9 @@
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
@@ -1400,6 +1428,9 @@
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2292,16 +2323,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2312,10 +2343,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2338,16 +2369,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2397,7 +2428,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2406,16 +2437,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2426,10 +2457,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2452,16 +2483,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2487,13 +2518,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2511,7 +2542,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2520,16 +2551,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2540,14 +2571,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2566,16 +2597,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2625,7 +2656,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2634,16 +2665,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2654,14 +2685,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2680,16 +2711,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2739,7 +2770,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2757,7 +2788,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2768,14 +2799,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2794,16 +2825,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2841,19 +2872,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2862,16 +2893,16 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2882,14 +2913,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2908,19 +2939,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2957,19 +2988,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2978,16 +3009,16 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2998,10 +3029,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3024,19 +3055,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3073,17 +3104,17 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3092,33 +3123,33 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
@@ -3140,19 +3171,19 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3201,7 +3232,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3210,30 +3241,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3256,13 +3287,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3313,7 +3344,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3331,7 +3362,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3342,14 +3373,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3368,16 +3399,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3415,19 +3446,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3436,16 +3467,16 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3456,10 +3487,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3482,19 +3513,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3519,13 +3550,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3543,7 +3574,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3552,30 +3583,30 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3598,19 +3629,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3620,7 +3651,7 @@
         <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>77</v>
@@ -3635,13 +3666,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3659,7 +3690,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3668,30 +3699,30 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3714,19 +3745,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3739,7 +3770,7 @@
         <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>77</v>
@@ -3775,7 +3806,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3784,30 +3815,30 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3830,16 +3861,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3853,7 +3884,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -3889,7 +3920,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3898,30 +3929,30 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3944,15 +3975,17 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4001,7 +4034,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4010,30 +4043,30 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4056,16 +4089,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4115,7 +4148,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4124,33 +4157,33 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4172,19 +4205,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4233,7 +4266,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4242,30 +4275,30 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4288,13 +4321,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4345,7 +4378,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4363,7 +4396,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4374,14 +4407,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4400,16 +4433,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4447,19 +4480,19 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4468,16 +4501,16 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4488,10 +4521,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4514,19 +4547,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4551,13 +4584,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4575,7 +4608,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4584,30 +4617,30 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4630,19 +4663,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4652,7 +4685,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -4667,13 +4700,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4691,7 +4724,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4700,30 +4733,30 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4746,19 +4779,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4771,7 +4804,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4807,7 +4840,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4816,30 +4849,30 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4862,16 +4895,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4885,7 +4918,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4921,7 +4954,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4930,30 +4963,30 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4976,15 +5009,17 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5033,7 +5068,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5042,30 +5077,30 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5088,16 +5123,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5147,7 +5182,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5156,30 +5191,30 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5202,15 +5237,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5259,7 +5296,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5268,16 +5305,16 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5288,10 +5325,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5314,16 +5351,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5373,7 +5410,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5382,16 +5419,16 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5402,14 +5439,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5428,15 +5465,17 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5485,7 +5524,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5494,16 +5533,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5514,14 +5553,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5540,16 +5579,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5599,7 +5638,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5608,16 +5647,16 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5628,10 +5667,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5654,16 +5693,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5689,13 +5728,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5713,7 +5752,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5722,19 +5761,19 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5742,14 +5781,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5768,16 +5807,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5803,32 +5842,32 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5836,30 +5875,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5882,15 +5921,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5915,13 +5956,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5939,7 +5980,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5948,34 +5989,34 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5994,17 +6035,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6029,13 +6072,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6053,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6062,34 +6105,34 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6108,15 +6151,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6165,7 +6210,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>87</v>
@@ -6174,30 +6219,30 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6220,16 +6265,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6279,7 +6324,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6288,30 +6333,30 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6334,16 +6379,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6393,7 +6438,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6402,30 +6447,30 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6448,15 +6493,17 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6505,7 +6552,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6514,19 +6561,19 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6534,10 +6581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6560,15 +6607,17 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6617,7 +6666,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6626,19 +6675,19 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6646,10 +6695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6672,13 +6721,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6729,7 +6778,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6738,16 +6787,16 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6758,10 +6807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6784,13 +6833,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6841,7 +6890,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6859,7 +6908,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6870,14 +6919,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6896,16 +6945,16 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6943,19 +6992,19 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6964,16 +7013,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6984,14 +7033,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7010,19 +7059,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7071,7 +7120,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7080,16 +7129,16 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7100,10 +7149,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7126,17 +7175,19 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7161,13 +7212,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7185,7 +7236,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7194,30 +7245,30 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7240,17 +7291,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7299,7 +7352,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>87</v>
@@ -7308,30 +7361,30 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7354,17 +7407,19 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7413,7 +7468,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7422,16 +7477,16 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7442,10 +7497,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7468,17 +7523,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7527,7 +7584,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7536,19 +7593,19 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7556,10 +7613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7582,16 +7639,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7617,13 +7674,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7641,7 +7698,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7650,30 +7707,30 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7696,16 +7753,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7755,7 +7812,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7764,19 +7821,19 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7784,10 +7841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7810,16 +7867,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7845,13 +7902,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7869,7 +7926,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7878,30 +7935,30 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7924,16 +7981,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7959,13 +8016,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7983,7 +8040,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7992,30 +8049,30 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8038,16 +8095,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8097,7 +8154,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8106,16 +8163,16 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8126,10 +8183,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8152,16 +8209,16 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8187,13 +8244,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8211,7 +8268,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8220,30 +8277,30 @@
         <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8266,17 +8323,19 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8325,7 +8384,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8334,16 +8393,16 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8354,10 +8413,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8380,15 +8439,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8413,13 +8474,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8437,7 +8498,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8446,30 +8507,30 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8492,15 +8553,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8549,7 +8612,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8558,30 +8621,30 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8604,13 +8667,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8661,7 +8724,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8670,16 +8733,16 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8690,10 +8753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8716,13 +8779,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8773,7 +8836,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8791,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8802,14 +8865,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8828,16 +8891,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8875,19 +8938,19 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8896,16 +8959,16 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8916,14 +8979,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8942,19 +9005,19 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9003,7 +9066,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9012,16 +9075,16 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9032,10 +9095,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9058,15 +9121,17 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9091,13 +9156,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9115,7 +9180,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9124,30 +9189,30 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9170,15 +9235,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9227,7 +9294,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -9236,16 +9303,16 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9256,10 +9323,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9282,19 +9349,19 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9343,7 +9410,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9352,16 +9419,16 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9372,10 +9439,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9398,16 +9465,16 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9433,13 +9500,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9457,7 +9524,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9466,22 +9533,22 @@
         <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-dmi-procedure.xlsx
+++ b/main/ig/StructureDefinition-dmi-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,17 +316,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Procedure.implicitRules</t>
   </si>
   <si>
@@ -346,9 +339,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Procedure.language</t>
   </si>
   <si>
@@ -426,6 +416,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Procedure.extension</t>
   </si>
   <si>
@@ -446,106 +439,109 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Procedure.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>External Identifiers for this procedure</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:type}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:idIntervention</t>
+  </si>
+  <si>
+    <t>idIntervention</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:idIntervention.id</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:idIntervention.extension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Procedure.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>External Identifiers for this procedure</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:type}
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
-  </si>
-  <si>
-    <t>Procedure.identifier:idIntervention</t>
-  </si>
-  <si>
-    <t>idIntervention</t>
-  </si>
-  <si>
-    <t>Procedure.identifier:idIntervention.id</t>
-  </si>
-  <si>
-    <t>Procedure.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Procedure.identifier:idIntervention.extension</t>
-  </si>
-  <si>
-    <t>Procedure.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -702,15 +698,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -739,10 +727,6 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
@@ -802,9 +786,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -843,9 +824,6 @@
     <t>A reference to a resource that contains details of the request for this procedure.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -937,9 +915,6 @@
     <t>.reason.Observation.value</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>Procedure.category</t>
   </si>
   <si>
@@ -947,9 +922,6 @@
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
@@ -1428,9 +1400,6 @@
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2323,16 +2292,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2343,10 +2312,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2369,16 +2338,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2428,7 +2397,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2437,16 +2406,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2457,10 +2426,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2483,16 +2452,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2518,32 +2487,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2551,16 +2520,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2571,14 +2540,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2597,16 +2566,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2656,7 +2625,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2665,16 +2634,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2685,14 +2654,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2711,16 +2680,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2770,7 +2739,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2788,7 +2757,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2799,14 +2768,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2825,16 +2794,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2872,19 +2841,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2893,16 +2862,16 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2913,14 +2882,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2939,19 +2908,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2988,19 +2957,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3009,16 +2978,16 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -3029,10 +2998,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3055,19 +3024,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3104,17 +3073,17 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3123,33 +3092,33 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
@@ -3171,19 +3140,19 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3232,7 +3201,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3241,30 +3210,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3287,13 +3256,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3344,7 +3313,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3362,7 +3331,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3373,14 +3342,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3399,16 +3368,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3446,19 +3415,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3467,16 +3436,16 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3487,10 +3456,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3513,19 +3482,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3550,63 +3519,63 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
+      <c r="AG15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3629,19 +3598,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3651,78 +3620,78 @@
         <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Y16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3745,19 +3714,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3770,75 +3739,75 @@
         <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="U17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3861,16 +3830,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3884,75 +3853,75 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="U18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3975,17 +3944,15 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4034,39 +4001,39 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4089,16 +4056,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4148,7 +4115,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4157,33 +4124,33 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4205,19 +4172,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4266,7 +4233,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4275,30 +4242,30 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK21" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4321,13 +4288,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4378,7 +4345,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4396,7 +4363,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4407,14 +4374,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4433,16 +4400,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4480,19 +4447,19 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4501,16 +4468,16 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4521,10 +4488,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4547,19 +4514,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4584,63 +4551,63 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4663,19 +4630,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4685,7 +4652,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -4700,63 +4667,63 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4779,19 +4746,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4804,75 +4771,75 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="U26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4895,16 +4862,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4918,75 +4885,75 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5009,17 +4976,15 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5068,39 +5033,39 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5123,16 +5088,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5182,7 +5147,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5191,30 +5156,30 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5237,17 +5202,15 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5296,7 +5259,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5305,16 +5268,16 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5325,10 +5288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5351,16 +5314,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5410,7 +5373,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5419,16 +5382,16 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5439,14 +5402,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5465,17 +5428,15 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5524,7 +5485,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5533,16 +5494,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK32" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5553,14 +5514,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5579,16 +5540,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5638,7 +5599,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5647,16 +5608,16 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5667,10 +5628,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5693,16 +5654,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5728,13 +5689,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5752,28 +5713,28 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK34" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="AL34" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5781,14 +5742,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5807,16 +5768,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5842,13 +5803,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5866,7 +5827,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5875,30 +5836,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5921,17 +5882,15 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5956,13 +5915,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5980,7 +5939,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5989,34 +5948,34 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6035,19 +5994,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N37" t="s" s="2">
         <v>297</v>
       </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6072,13 +6029,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6096,43 +6053,43 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AM37" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6151,17 +6108,15 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6210,39 +6165,39 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6265,16 +6220,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6324,39 +6279,39 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6379,16 +6334,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6438,39 +6393,39 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6493,17 +6448,15 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6552,7 +6505,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6561,19 +6514,19 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6581,10 +6534,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6607,17 +6560,15 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6666,7 +6617,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6675,19 +6626,19 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6695,10 +6646,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6721,13 +6672,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6778,7 +6729,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6787,16 +6738,16 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK43" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6807,10 +6758,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6833,13 +6784,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6890,7 +6841,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6859,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6919,14 +6870,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6945,16 +6896,16 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6992,19 +6943,19 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7013,16 +6964,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7033,14 +6984,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7059,19 +7010,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7120,7 +7071,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7129,16 +7080,16 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7149,10 +7100,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7175,19 +7126,17 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7212,13 +7161,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7236,39 +7185,39 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7291,19 +7240,17 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7352,39 +7299,39 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7407,19 +7354,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7468,7 +7413,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7477,16 +7422,16 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7497,10 +7442,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7523,19 +7468,17 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7584,7 +7527,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7593,19 +7536,19 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7613,10 +7556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7639,16 +7582,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7674,13 +7617,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7698,7 +7641,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7707,30 +7650,30 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK51" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7753,16 +7696,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7812,7 +7755,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7821,19 +7764,19 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK52" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7841,10 +7784,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7867,16 +7810,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7902,13 +7845,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7926,7 +7869,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7935,30 +7878,30 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7981,16 +7924,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8016,13 +7959,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8040,7 +7983,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8049,30 +7992,30 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8095,16 +8038,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8154,7 +8097,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8163,16 +8106,16 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8183,10 +8126,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8209,16 +8152,16 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8244,13 +8187,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8268,7 +8211,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8277,30 +8220,30 @@
         <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8323,19 +8266,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8384,7 +8325,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8393,16 +8334,16 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8413,10 +8354,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8439,17 +8380,15 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8474,13 +8413,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8498,7 +8437,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8507,30 +8446,30 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8553,17 +8492,15 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8612,7 +8549,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8621,30 +8558,30 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ59" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK59" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8667,13 +8604,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8724,7 +8661,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8733,16 +8670,16 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8753,10 +8690,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8779,13 +8716,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8836,7 +8773,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8854,7 +8791,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8865,14 +8802,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8891,16 +8828,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8938,19 +8875,19 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8959,16 +8896,16 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8979,14 +8916,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9005,19 +8942,19 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9066,7 +9003,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9075,16 +9012,16 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9095,10 +9032,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9121,17 +9058,15 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9156,13 +9091,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9180,7 +9115,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9189,30 +9124,30 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ64" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9235,17 +9170,15 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9294,7 +9227,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -9303,16 +9236,16 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ65" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9323,10 +9256,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9349,19 +9282,19 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9410,7 +9343,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9419,16 +9352,16 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9439,10 +9372,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9465,16 +9398,16 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9500,13 +9433,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9524,7 +9457,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9533,22 +9466,22 @@
         <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-dmi-procedure.xlsx
+++ b/main/ig/StructureDefinition-dmi-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-procedure.xlsx
+++ b/main/ig/StructureDefinition-dmi-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Procedure.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Procedure.language</t>
   </si>
   <si>
@@ -416,9 +426,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Procedure.extension</t>
   </si>
   <si>
@@ -439,6 +446,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -485,9 +502,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -525,9 +539,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Procedure.identifier:idIntervention.extension</t>
   </si>
   <si>
@@ -535,13 +546,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -698,7 +702,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -727,6 +739,10 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
@@ -786,6 +802,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -824,6 +843,9 @@
     <t>A reference to a resource that contains details of the request for this procedure.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -915,6 +937,9 @@
     <t>.reason.Observation.value</t>
   </si>
   <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
     <t>Procedure.category</t>
   </si>
   <si>
@@ -922,6 +947,9 @@
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
@@ -1400,6 +1428,9 @@
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2292,16 +2323,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2312,10 +2343,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2338,16 +2369,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2397,7 +2428,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2406,16 +2437,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2426,10 +2457,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2452,16 +2483,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2487,13 +2518,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2511,7 +2542,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2520,16 +2551,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2540,14 +2571,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2566,16 +2597,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2625,7 +2656,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2634,16 +2665,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2654,14 +2685,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2680,16 +2711,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2739,7 +2770,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2757,7 +2788,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2768,14 +2799,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2794,16 +2825,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2841,19 +2872,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2862,16 +2893,16 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2882,14 +2913,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2908,19 +2939,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2957,19 +2988,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2978,16 +3009,16 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2998,10 +3029,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3024,19 +3055,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3073,17 +3104,17 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3092,33 +3123,33 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
@@ -3140,19 +3171,19 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3201,7 +3232,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3210,30 +3241,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3256,13 +3287,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3313,7 +3344,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3331,7 +3362,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3342,14 +3373,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3368,16 +3399,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3415,19 +3446,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3436,16 +3467,16 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3456,10 +3487,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3482,19 +3513,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3519,13 +3550,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3543,7 +3574,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3552,30 +3583,30 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3598,19 +3629,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3620,7 +3651,7 @@
         <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>77</v>
@@ -3635,13 +3666,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3659,7 +3690,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3668,30 +3699,30 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3714,19 +3745,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3739,7 +3770,7 @@
         <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>77</v>
@@ -3775,7 +3806,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3784,30 +3815,30 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3830,16 +3861,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3853,7 +3884,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -3889,7 +3920,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3898,30 +3929,30 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3944,15 +3975,17 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4001,7 +4034,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4010,30 +4043,30 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4056,16 +4089,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4115,7 +4148,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4124,33 +4157,33 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4172,19 +4205,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4233,7 +4266,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4242,30 +4275,30 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4288,13 +4321,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4345,7 +4378,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4363,7 +4396,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4374,14 +4407,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4400,16 +4433,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4447,19 +4480,19 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4468,16 +4501,16 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4488,10 +4521,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4514,19 +4547,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4551,13 +4584,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4575,7 +4608,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4584,30 +4617,30 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4630,19 +4663,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4652,7 +4685,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -4667,13 +4700,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4691,7 +4724,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4700,30 +4733,30 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4746,19 +4779,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4771,7 +4804,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4807,7 +4840,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4816,30 +4849,30 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4862,16 +4895,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4885,7 +4918,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4921,7 +4954,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4930,30 +4963,30 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4976,15 +5009,17 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5033,7 +5068,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5042,30 +5077,30 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5088,16 +5123,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5147,7 +5182,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5156,30 +5191,30 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5202,15 +5237,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5259,7 +5296,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5268,16 +5305,16 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5288,10 +5325,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5314,16 +5351,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5373,7 +5410,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5382,16 +5419,16 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5402,14 +5439,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5428,15 +5465,17 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5485,7 +5524,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5494,16 +5533,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5514,14 +5553,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5540,16 +5579,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5599,7 +5638,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5608,16 +5647,16 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5628,10 +5667,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5654,16 +5693,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5689,13 +5728,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5713,7 +5752,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5722,19 +5761,19 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5742,14 +5781,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5768,16 +5807,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5803,32 +5842,32 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5836,30 +5875,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5882,15 +5921,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5915,13 +5956,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5939,7 +5980,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5948,34 +5989,34 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5994,17 +6035,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6029,13 +6072,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6053,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6062,34 +6105,34 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6108,15 +6151,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6165,7 +6210,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>87</v>
@@ -6174,30 +6219,30 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6220,16 +6265,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6279,7 +6324,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6288,30 +6333,30 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6334,16 +6379,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6393,7 +6438,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6402,30 +6447,30 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6448,15 +6493,17 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6505,7 +6552,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6514,19 +6561,19 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6534,10 +6581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6560,15 +6607,17 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6617,7 +6666,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6626,19 +6675,19 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6646,10 +6695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6672,13 +6721,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6729,7 +6778,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6738,16 +6787,16 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6758,10 +6807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6784,13 +6833,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6841,7 +6890,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6859,7 +6908,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6870,14 +6919,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6896,16 +6945,16 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6943,19 +6992,19 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6964,16 +7013,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6984,14 +7033,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7010,19 +7059,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7071,7 +7120,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7080,16 +7129,16 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7100,10 +7149,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7126,17 +7175,19 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7161,13 +7212,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7185,7 +7236,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7194,30 +7245,30 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7240,17 +7291,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7299,7 +7352,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>87</v>
@@ -7308,30 +7361,30 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7354,17 +7407,19 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7413,7 +7468,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7422,16 +7477,16 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7442,10 +7497,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7468,17 +7523,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7527,7 +7584,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7536,19 +7593,19 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7556,10 +7613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7582,16 +7639,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7617,13 +7674,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7641,7 +7698,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7650,30 +7707,30 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7696,16 +7753,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7755,7 +7812,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7764,19 +7821,19 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7784,10 +7841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7810,16 +7867,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7845,13 +7902,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7869,7 +7926,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7878,30 +7935,30 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7924,16 +7981,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7959,13 +8016,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7983,7 +8040,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7992,30 +8049,30 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8038,16 +8095,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8097,7 +8154,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8106,16 +8163,16 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8126,10 +8183,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8152,16 +8209,16 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8187,13 +8244,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8211,7 +8268,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8220,30 +8277,30 @@
         <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8266,17 +8323,19 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8325,7 +8384,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8334,16 +8393,16 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8354,10 +8413,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8380,15 +8439,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8413,13 +8474,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8437,7 +8498,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8446,30 +8507,30 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8492,15 +8553,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8549,7 +8612,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8558,30 +8621,30 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8604,13 +8667,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8661,7 +8724,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8670,16 +8733,16 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8690,10 +8753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8716,13 +8779,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8773,7 +8836,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8791,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8802,14 +8865,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8828,16 +8891,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8875,19 +8938,19 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8896,16 +8959,16 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8916,14 +8979,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8942,19 +9005,19 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9003,7 +9066,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9012,16 +9075,16 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9032,10 +9095,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9058,15 +9121,17 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9091,13 +9156,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9115,7 +9180,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9124,30 +9189,30 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9170,15 +9235,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9227,7 +9294,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -9236,16 +9303,16 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9256,10 +9323,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9282,19 +9349,19 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9343,7 +9410,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9352,16 +9419,16 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9372,10 +9439,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9398,16 +9465,16 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9433,13 +9500,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9457,7 +9524,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9466,22 +9533,22 @@
         <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
